--- a/output/pdf_financials_xlsx/GGX.xlsx
+++ b/output/pdf_financials_xlsx/GGX.xlsx
@@ -4468,37 +4468,37 @@
         <v>0.281595</v>
       </c>
       <c r="C92" s="3" t="n">
-        <v>0.281595</v>
+        <v>0.025296</v>
       </c>
       <c r="D92" s="3" t="n">
-        <v>0</v>
+        <v>0.07499699999999999</v>
       </c>
       <c r="E92" s="3" t="n">
-        <v>0</v>
+        <v>0.129492</v>
       </c>
       <c r="F92" s="3" t="n">
-        <v>0</v>
+        <v>0.052512</v>
       </c>
       <c r="G92" s="3" t="n">
-        <v>0</v>
+        <v>0.057801</v>
       </c>
       <c r="H92" s="3" t="n">
-        <v>0</v>
+        <v>0.083815</v>
       </c>
       <c r="I92" s="3" t="n">
-        <v>0</v>
+        <v>0.041724</v>
       </c>
       <c r="J92" s="3" t="n">
-        <v>0</v>
+        <v>0.034491</v>
       </c>
       <c r="K92" s="3" t="n">
-        <v>0</v>
+        <v>0.00039</v>
       </c>
       <c r="L92" s="3" t="n">
-        <v>0</v>
+        <v>0.000245</v>
       </c>
       <c r="M92" s="3" t="n">
-        <v>0</v>
+        <v>0.000245</v>
       </c>
     </row>
     <row r="93">
@@ -7496,7 +7496,11 @@
           <t>Share Purchase Warrants Reserve</t>
         </is>
       </c>
-      <c r="D17" t="inlineStr"/>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E17" t="inlineStr">
         <is>
           <t>-</t>
@@ -13892,7 +13896,11 @@
           <t>Share Purchase Warrants Reserve</t>
         </is>
       </c>
-      <c r="D102" t="inlineStr"/>
+      <c r="D102" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E102" t="inlineStr">
         <is>
           <t>-</t>
@@ -15480,7 +15488,11 @@
           <t>Share Purchase Warrants Reserve 2</t>
         </is>
       </c>
-      <c r="D123" t="inlineStr"/>
+      <c r="D123" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E123" t="inlineStr">
         <is>
           <t>-</t>
@@ -16466,7 +16478,11 @@
           <t>Share Purchase Warrants Reserve 2</t>
         </is>
       </c>
-      <c r="D136" t="inlineStr"/>
+      <c r="D136" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E136" t="inlineStr">
         <is>
           <t>-</t>

--- a/output/pdf_financials_xlsx/GGX.xlsx
+++ b/output/pdf_financials_xlsx/GGX.xlsx
@@ -889,7 +889,7 @@
         <v>0</v>
       </c>
       <c r="D12" s="3" t="n">
-        <v>0</v>
+        <v>0.00055</v>
       </c>
       <c r="E12" s="3" t="n">
         <v>0</v>
@@ -1600,7 +1600,7 @@
         <v>-1.216104</v>
       </c>
       <c r="D27" s="3" t="n">
-        <v>-0.171154</v>
+        <v>-0.171704</v>
       </c>
       <c r="E27" s="3" t="n">
         <v>-1.803916</v>
@@ -1686,7 +1686,7 @@
         <v>-1.216104</v>
       </c>
       <c r="D29" s="3" t="n">
-        <v>-0.171154</v>
+        <v>-0.171704</v>
       </c>
       <c r="E29" s="3" t="n">
         <v>-1.801536</v>
@@ -1907,40 +1907,40 @@
         </is>
       </c>
       <c r="B34" s="3" t="n">
-        <v>0</v>
+        <v>7.4e-05</v>
       </c>
       <c r="C34" s="3" t="n">
         <v>0</v>
       </c>
       <c r="D34" s="3" t="n">
-        <v>0</v>
+        <v>0.438703</v>
       </c>
       <c r="E34" s="3" t="n">
-        <v>0</v>
+        <v>0.058679</v>
       </c>
       <c r="F34" s="3" t="n">
-        <v>0</v>
+        <v>0.214384</v>
       </c>
       <c r="G34" s="3" t="n">
-        <v>0</v>
+        <v>0.010589</v>
       </c>
       <c r="H34" s="3" t="n">
-        <v>0</v>
+        <v>0.001792</v>
       </c>
       <c r="I34" s="3" t="n">
-        <v>0</v>
+        <v>0.008425999999999999</v>
       </c>
       <c r="J34" s="3" t="n">
-        <v>0</v>
+        <v>0.003083</v>
       </c>
       <c r="K34" s="3" t="n">
-        <v>0</v>
+        <v>4.4e-05</v>
       </c>
       <c r="L34" s="3" t="n">
-        <v>0</v>
+        <v>0.000287</v>
       </c>
       <c r="M34" s="3" t="n">
-        <v>0</v>
+        <v>0.000118</v>
       </c>
     </row>
     <row r="35">
@@ -1993,40 +1993,40 @@
         </is>
       </c>
       <c r="B36" s="3" t="n">
-        <v>0</v>
+        <v>7.4e-05</v>
       </c>
       <c r="C36" s="3" t="n">
         <v>0</v>
       </c>
       <c r="D36" s="3" t="n">
-        <v>0</v>
+        <v>0.438703</v>
       </c>
       <c r="E36" s="3" t="n">
-        <v>0</v>
+        <v>0.058679</v>
       </c>
       <c r="F36" s="3" t="n">
-        <v>0.078817</v>
+        <v>0.293201</v>
       </c>
       <c r="G36" s="3" t="n">
-        <v>0.049556</v>
+        <v>0.060145</v>
       </c>
       <c r="H36" s="3" t="n">
-        <v>0.080248</v>
+        <v>0.08204</v>
       </c>
       <c r="I36" s="3" t="n">
-        <v>0.03632</v>
+        <v>0.044746</v>
       </c>
       <c r="J36" s="3" t="n">
-        <v>0.002645</v>
+        <v>0.005728</v>
       </c>
       <c r="K36" s="3" t="n">
-        <v>0</v>
+        <v>4.4e-05</v>
       </c>
       <c r="L36" s="3" t="n">
-        <v>0.819</v>
+        <v>0.819287</v>
       </c>
       <c r="M36" s="3" t="n">
-        <v>0</v>
+        <v>0.000118</v>
       </c>
     </row>
     <row r="37">
@@ -2509,40 +2509,40 @@
         </is>
       </c>
       <c r="B48" s="3" t="n">
-        <v>0.005074</v>
+        <v>0.005</v>
       </c>
       <c r="C48" s="3" t="n">
         <v>0</v>
       </c>
       <c r="D48" s="3" t="n">
-        <v>0.44411</v>
+        <v>0.005407</v>
       </c>
       <c r="E48" s="3" t="n">
-        <v>0.149447</v>
+        <v>0.090768</v>
       </c>
       <c r="F48" s="3" t="n">
-        <v>0.297792</v>
+        <v>0.083408</v>
       </c>
       <c r="G48" s="3" t="n">
-        <v>0.047237</v>
+        <v>0.036648</v>
       </c>
       <c r="H48" s="3" t="n">
-        <v>0.033637</v>
+        <v>0.031845</v>
       </c>
       <c r="I48" s="3" t="n">
-        <v>0.024918</v>
+        <v>0.016492</v>
       </c>
       <c r="J48" s="3" t="n">
-        <v>0.010806</v>
+        <v>0.007723</v>
       </c>
       <c r="K48" s="3" t="n">
-        <v>0.003361</v>
+        <v>0.003317</v>
       </c>
       <c r="L48" s="3" t="n">
-        <v>0.003432</v>
+        <v>0.003145</v>
       </c>
       <c r="M48" s="3" t="n">
-        <v>0.000118</v>
+        <v>0</v>
       </c>
     </row>
     <row r="49">
@@ -6480,7 +6480,7 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>Cash</t>
+          <t>CashAndCashEquivalents</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
@@ -13210,7 +13210,7 @@
       </c>
       <c r="D93" t="inlineStr">
         <is>
-          <t>Cash</t>
+          <t>CashAndCashEquivalents</t>
         </is>
       </c>
       <c r="E93" t="inlineStr">
@@ -15108,7 +15108,7 @@
       </c>
       <c r="D118" t="inlineStr">
         <is>
-          <t>Cash</t>
+          <t>CashAndCashEquivalents</t>
         </is>
       </c>
       <c r="E118" t="inlineStr">
@@ -17162,7 +17162,7 @@
       </c>
       <c r="D145" t="inlineStr">
         <is>
-          <t>Cash</t>
+          <t>CashAndCashEquivalents</t>
         </is>
       </c>
       <c r="E145" s="5" t="n">
@@ -25862,7 +25862,11 @@
           <t>Reclamation deposit</t>
         </is>
       </c>
-      <c r="D262" t="inlineStr"/>
+      <c r="D262" t="inlineStr">
+        <is>
+          <t>ChangeInRestrictedCash</t>
+        </is>
+      </c>
       <c r="E262" s="5" t="n">
         <v>-0.0139</v>
       </c>
@@ -31488,7 +31492,7 @@
       </c>
       <c r="D339" t="inlineStr">
         <is>
-          <t>InterestIncome</t>
+          <t>InterestIncomeNonOperating</t>
         </is>
       </c>
       <c r="E339" t="inlineStr">

--- a/output/pdf_financials_xlsx/GGX.xlsx
+++ b/output/pdf_financials_xlsx/GGX.xlsx
@@ -4823,37 +4823,37 @@
         <v>-0.044584</v>
       </c>
       <c r="C101" s="3" t="n">
-        <v>0.02079</v>
+        <v>0.099982</v>
       </c>
       <c r="D101" s="3" t="n">
-        <v>0</v>
+        <v>-0.000708</v>
       </c>
       <c r="E101" s="3" t="n">
-        <v>0</v>
+        <v>-0.009636</v>
       </c>
       <c r="F101" s="3" t="n">
-        <v>0</v>
+        <v>-0.049212</v>
       </c>
       <c r="G101" s="3" t="n">
-        <v>0</v>
+        <v>0.027607</v>
       </c>
       <c r="H101" s="3" t="n">
-        <v>0</v>
+        <v>0.026934</v>
       </c>
       <c r="I101" s="3" t="n">
-        <v>0</v>
+        <v>-0.006778</v>
       </c>
       <c r="J101" s="3" t="n">
-        <v>0</v>
+        <v>0.008769000000000001</v>
       </c>
       <c r="K101" s="3" t="n">
-        <v>0</v>
+        <v>0.004406</v>
       </c>
       <c r="L101" s="3" t="n">
-        <v>0</v>
+        <v>0.000172</v>
       </c>
       <c r="M101" s="3" t="n">
-        <v>0</v>
+        <v>0.003925</v>
       </c>
     </row>
     <row r="102">
@@ -5271,7 +5271,7 @@
         <v>0</v>
       </c>
       <c r="I111" s="3" t="n">
-        <v>0</v>
+        <v>-0.016077</v>
       </c>
       <c r="J111" s="3" t="n">
         <v>0</v>
@@ -5400,7 +5400,7 @@
         <v>0</v>
       </c>
       <c r="I114" s="3" t="n">
-        <v>0</v>
+        <v>-0.07839</v>
       </c>
       <c r="J114" s="3" t="n">
         <v>0</v>
@@ -5434,28 +5434,28 @@
         <v>0</v>
       </c>
       <c r="F115" s="3" t="n">
-        <v>0</v>
+        <v>0.518268</v>
       </c>
       <c r="G115" s="3" t="n">
-        <v>0</v>
+        <v>0.127175</v>
       </c>
       <c r="H115" s="3" t="n">
-        <v>0</v>
+        <v>0.035416</v>
       </c>
       <c r="I115" s="3" t="n">
-        <v>0</v>
+        <v>0.488944</v>
       </c>
       <c r="J115" s="3" t="n">
-        <v>0</v>
+        <v>0.03145</v>
       </c>
       <c r="K115" s="3" t="n">
-        <v>0</v>
+        <v>0.00299</v>
       </c>
       <c r="L115" s="3" t="n">
-        <v>0</v>
+        <v>0.02487</v>
       </c>
       <c r="M115" s="3" t="n">
-        <v>0</v>
+        <v>1.111709</v>
       </c>
     </row>
     <row r="116">
@@ -6294,7 +6294,7 @@
         <v>0</v>
       </c>
       <c r="I134" s="3" t="n">
-        <v>0</v>
+        <v>-0.016077</v>
       </c>
       <c r="J134" s="3" t="n">
         <v>0</v>
@@ -6339,7 +6339,7 @@
         <v>-1.377526</v>
       </c>
       <c r="I135" s="3" t="n">
-        <v>-1.330894</v>
+        <v>-1.346971</v>
       </c>
       <c r="J135" s="3" t="n">
         <v>-0.800769</v>
@@ -18492,7 +18492,11 @@
           <t>GST Recoverable</t>
         </is>
       </c>
-      <c r="D163" t="inlineStr"/>
+      <c r="D163" t="inlineStr">
+        <is>
+          <t>ChangeInReceivables</t>
+        </is>
+      </c>
       <c r="E163" t="inlineStr">
         <is>
           <t>-</t>
@@ -19186,7 +19190,11 @@
           <t>Proceeds from Sale of Marketable Securities</t>
         </is>
       </c>
-      <c r="D173" t="inlineStr"/>
+      <c r="D173" t="inlineStr">
+        <is>
+          <t>SaleOfInvestment</t>
+        </is>
+      </c>
       <c r="E173" t="inlineStr">
         <is>
           <t>-</t>
@@ -19626,7 +19634,11 @@
           <t>Shares Issued for Cash</t>
         </is>
       </c>
-      <c r="D179" t="inlineStr"/>
+      <c r="D179" t="inlineStr">
+        <is>
+          <t>CommonStockIssuance</t>
+        </is>
+      </c>
       <c r="E179" t="inlineStr">
         <is>
           <t>-</t>
@@ -20782,7 +20794,11 @@
           <t>Proceeds from Sale of Marketable Securities</t>
         </is>
       </c>
-      <c r="D195" t="inlineStr"/>
+      <c r="D195" t="inlineStr">
+        <is>
+          <t>SaleOfInvestment</t>
+        </is>
+      </c>
       <c r="E195" t="inlineStr">
         <is>
           <t>-</t>
@@ -20854,7 +20870,11 @@
           <t>Purchases of Marketable Securities</t>
         </is>
       </c>
-      <c r="D196" t="inlineStr"/>
+      <c r="D196" t="inlineStr">
+        <is>
+          <t>PurchaseOfInvestment</t>
+        </is>
+      </c>
       <c r="E196" t="inlineStr">
         <is>
           <t>-</t>
@@ -20930,7 +20950,11 @@
           <t>Purchase of Equipment</t>
         </is>
       </c>
-      <c r="D197" t="inlineStr"/>
+      <c r="D197" t="inlineStr">
+        <is>
+          <t>PurchaseOfPPE</t>
+        </is>
+      </c>
       <c r="E197" t="inlineStr">
         <is>
           <t>-</t>
@@ -22404,7 +22428,11 @@
           <t>Proceeds from the Sale of Marketable Securities</t>
         </is>
       </c>
-      <c r="D217" t="inlineStr"/>
+      <c r="D217" t="inlineStr">
+        <is>
+          <t>SaleOfInvestment</t>
+        </is>
+      </c>
       <c r="E217" t="inlineStr">
         <is>
           <t>-</t>
@@ -24540,7 +24568,11 @@
           <t>Fair Value of Warrants Issued for Private Placement</t>
         </is>
       </c>
-      <c r="D245" t="inlineStr"/>
+      <c r="D245" t="inlineStr">
+        <is>
+          <t>CommonStockIssuance</t>
+        </is>
+      </c>
       <c r="E245" t="inlineStr">
         <is>
           <t>-</t>
